--- a/Screenshot_Watchlist_Oct2026.xlsx
+++ b/Screenshot_Watchlist_Oct2026.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Key &amp; Sources" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Watchlist!$A$1:$Q$102</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Watchlist!$A$1:$Q$116</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="536">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -788,6 +788,9 @@
     <t xml:space="preserve">137K</t>
   </si>
   <si>
+    <t xml:space="preserve">Twisty Mystery Thrillers (collage, no caption); Psychological Experiments &amp; Mind Games (collage, no caption)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Single-room puzzle thriller.</t>
   </si>
   <si>
@@ -812,18 +815,21 @@
     <t xml:space="preserve">908K</t>
   </si>
   <si>
+    <t xml:space="preserve">Best Space Adventure Films; Lonely Astronauts &amp; Silent Missions Beyond Earth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91-minute edge-of-seat survival thriller.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">707K</t>
+  </si>
+  <si>
     <t xml:space="preserve">Best Space Adventure Films</t>
   </si>
   <si>
-    <t xml:space="preserve">91-minute edge-of-seat survival thriller.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">707K</t>
-  </si>
-  <si>
     <t xml:space="preserve">Alien prequel; some horror.</t>
   </si>
   <si>
@@ -1370,10 +1376,142 @@
     <t xml:space="preserve">Netflix India audio includes Hindi, Tamil, Telugu.</t>
   </si>
   <si>
+    <t xml:space="preserve">The Experiment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drama, Psychological Thriller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psychological Experiments &amp; Mind Games (collage, no caption)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrien Brody, Forest Whitaker; remake of the German Das Experiment (2001), inspired by the Stanford prison study.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Stanford Prison Experiment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drama, Psychological Thriller, History</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">True-story drama; rent only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Killing Room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secret government experiment thriller; no India listing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Wave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aka Die Welle — a teacher's classroom experiment turns into a movement (not the 2015 Norwegian disaster film).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Philosophers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aka After the Dark — a class acts out a survival thought experiment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Circle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 strangers must vote on who dies next.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sci-Fi, Thriller, Horror</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Artifice Girl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talky indie AI thriller; no India listing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lonely Astronauts &amp; Silent Missions Beyond Earth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Rockwell; excellent twist-driven sci-fi, but rent only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Midnight Sky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">George Clooney; slow-burn. Netflix India audio includes Hindi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spaceman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Sandler; slow and melancholic. Netflix India audio includes Hindi, Tamil, Telugu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stowaway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sci-Fi, Thriller, Drama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moral-dilemma survival thriller on a Mars mission. Netflix India audio includes Hindi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solaris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steven Soderbergh's version with George Clooney (Tarkovsky's 1972 original also exists); slow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approaching the Unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5K</t>
+  </si>
+  <si>
     <t xml:space="preserve">How to read this sheet</t>
   </si>
   <si>
-    <t xml:space="preserve">101 unique titles from your 10 screenshots (one image was posted twice; 5 titles appear in two lists — the topic column shows both). Streaming data checked on JustWatch India, 27–28 Oct 2026; OTT catalogues change often.</t>
+    <t xml:space="preserve">115 unique titles from your 12 screenshots (one image was posted twice; 9 titles appear in two lists — the topic column shows both). Streaming data checked on JustWatch India, 27–28 Oct 2026; OTT catalogues change often.</t>
   </si>
   <si>
     <t xml:space="preserve">Hindi is listed in the Netflix India title page's audio list, or the platform / release coverage announced a Hindi version (The Boys, Jack Ryan, The Terminal List, Unmadham).</t>
@@ -1424,7 +1562,7 @@
     <t xml:space="preserve">Status, Your Rating (0–10) and Suggested Priority have dropdowns / checks so you can keep using this as a tracker.</t>
   </si>
   <si>
-    <t xml:space="preserve">Link to the title's JustWatch India page (Netflix page for Money Heist; JustWatch US for The Treatment, which has no India page).</t>
+    <t xml:space="preserve">Link to the title's JustWatch India page. Netflix India page for Money Heist, Tau and Spaceman; JustWatch US/Austria for The Treatment, The Killing Room and The Artifice Girl, which have no India page.</t>
   </si>
   <si>
     <t xml:space="preserve">Summary</t>
@@ -1457,7 +1595,7 @@
     <t xml:space="preserve">Already watched</t>
   </si>
   <si>
-    <t xml:space="preserve">Titles per screenshot (5 titles are counted twice)</t>
+    <t xml:space="preserve">Titles per screenshot (9 titles are counted twice)</t>
   </si>
   <si>
     <t xml:space="preserve">Sources</t>
@@ -2140,7 +2278,7 @@
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q102"/>
+  <dimension ref="A1:Q116"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -4812,7 +4950,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
@@ -4847,7 +4985,7 @@
         <v>37</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>27</v>
@@ -4857,7 +4995,7 @@
         <v>28</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q53" s="6" t="s">
         <v>30</v>
@@ -4868,7 +5006,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>43</v>
@@ -4877,7 +5015,7 @@
         <v>19</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>64</v>
@@ -4886,7 +5024,7 @@
         <v>7.1</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>126</v>
@@ -4908,18 +5046,18 @@
         <v>28</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q54" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>87</v>
@@ -4931,13 +5069,13 @@
         <v>20</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G55" s="5" t="n">
         <v>7.7</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>34</v>
@@ -4949,7 +5087,7 @@
         <v>25</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M55" s="2" t="s">
         <v>27</v>
@@ -4959,7 +5097,7 @@
         <v>50</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q55" s="6" t="s">
         <v>30</v>
@@ -4970,7 +5108,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>217</v>
@@ -4988,7 +5126,7 @@
         <v>7</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>34</v>
@@ -5000,7 +5138,7 @@
         <v>37</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="M56" s="2" t="s">
         <v>27</v>
@@ -5010,7 +5148,7 @@
         <v>60</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q56" s="6" t="s">
         <v>30</v>
@@ -5021,10 +5159,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>19</v>
@@ -5033,13 +5171,13 @@
         <v>20</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G57" s="5" t="n">
         <v>7.2</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>23</v>
@@ -5051,7 +5189,7 @@
         <v>37</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="M57" s="2" t="s">
         <v>27</v>
@@ -5065,12 +5203,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>106</v>
@@ -5100,7 +5238,7 @@
         <v>37</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M58" s="2" t="s">
         <v>36</v>
@@ -5110,18 +5248,18 @@
         <v>37</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q58" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>130</v>
@@ -5139,7 +5277,7 @@
         <v>6.5</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>23</v>
@@ -5151,7 +5289,7 @@
         <v>37</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M59" s="2" t="s">
         <v>27</v>
@@ -5161,7 +5299,7 @@
         <v>28</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q59" s="6" t="s">
         <v>30</v>
@@ -5172,7 +5310,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>155</v>
@@ -5184,13 +5322,13 @@
         <v>20</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G60" s="5" t="n">
         <v>7.3</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>23</v>
@@ -5202,7 +5340,7 @@
         <v>59</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="M60" s="2" t="s">
         <v>27</v>
@@ -5212,7 +5350,7 @@
         <v>28</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q60" s="6" t="s">
         <v>30</v>
@@ -5223,7 +5361,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>139</v>
@@ -5235,25 +5373,25 @@
         <v>20</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G61" s="5" t="n">
         <v>7</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>34</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="M61" s="2" t="s">
         <v>27</v>
@@ -5272,10 +5410,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>19</v>
@@ -5284,13 +5422,13 @@
         <v>20</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G62" s="5" t="n">
         <v>8.3</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>126</v>
@@ -5302,7 +5440,7 @@
         <v>25</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>27</v>
@@ -5312,7 +5450,7 @@
         <v>28</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q62" s="6" t="s">
         <v>30</v>
@@ -5323,10 +5461,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>19</v>
@@ -5341,7 +5479,7 @@
         <v>7.3</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>23</v>
@@ -5353,7 +5491,7 @@
         <v>25</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>27</v>
@@ -5363,7 +5501,7 @@
         <v>28</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q63" s="6" t="s">
         <v>30</v>
@@ -5374,7 +5512,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>43</v>
@@ -5392,7 +5530,7 @@
         <v>7.2</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>126</v>
@@ -5404,7 +5542,7 @@
         <v>37</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>27</v>
@@ -5414,7 +5552,7 @@
         <v>28</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q64" s="6" t="s">
         <v>30</v>
@@ -5425,7 +5563,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>63</v>
@@ -5434,7 +5572,7 @@
         <v>19</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>212</v>
@@ -5443,7 +5581,7 @@
         <v>7.5</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I65" s="4" t="s">
         <v>126</v>
@@ -5455,7 +5593,7 @@
         <v>37</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M65" s="2" t="s">
         <v>27</v>
@@ -5465,7 +5603,7 @@
         <v>28</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q65" s="6" t="s">
         <v>30</v>
@@ -5476,10 +5614,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>19</v>
@@ -5488,13 +5626,13 @@
         <v>20</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G66" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>126</v>
@@ -5506,7 +5644,7 @@
         <v>37</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M66" s="2" t="s">
         <v>27</v>
@@ -5525,16 +5663,16 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>160</v>
@@ -5555,7 +5693,7 @@
         <v>37</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M67" s="2" t="s">
         <v>27</v>
@@ -5565,7 +5703,7 @@
         <v>28</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q67" s="6" t="s">
         <v>30</v>
@@ -5576,7 +5714,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>43</v>
@@ -5588,13 +5726,13 @@
         <v>20</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G68" s="5" t="n">
         <v>7.4</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>23</v>
@@ -5606,7 +5744,7 @@
         <v>37</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M68" s="2" t="s">
         <v>27</v>
@@ -5616,7 +5754,7 @@
         <v>60</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q68" s="6" t="s">
         <v>30</v>
@@ -5627,7 +5765,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>217</v>
@@ -5645,7 +5783,7 @@
         <v>7.4</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>23</v>
@@ -5657,7 +5795,7 @@
         <v>37</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M69" s="2" t="s">
         <v>27</v>
@@ -5676,10 +5814,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>19</v>
@@ -5688,13 +5826,13 @@
         <v>211</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G70" s="5" t="n">
         <v>7.1</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>126</v>
@@ -5706,7 +5844,7 @@
         <v>37</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M70" s="2" t="s">
         <v>27</v>
@@ -5716,7 +5854,7 @@
         <v>28</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q70" s="6" t="s">
         <v>30</v>
@@ -5727,7 +5865,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>167</v>
@@ -5739,13 +5877,13 @@
         <v>20</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G71" s="5" t="n">
         <v>6.9</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>126</v>
@@ -5757,7 +5895,7 @@
         <v>37</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M71" s="2" t="s">
         <v>27</v>
@@ -5767,7 +5905,7 @@
         <v>28</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q71" s="6" t="s">
         <v>30</v>
@@ -5778,7 +5916,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>139</v>
@@ -5796,7 +5934,7 @@
         <v>6.3</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>74</v>
@@ -5808,7 +5946,7 @@
         <v>37</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M72" s="2" t="s">
         <v>27</v>
@@ -5818,7 +5956,7 @@
         <v>28</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q72" s="6" t="s">
         <v>30</v>
@@ -5829,7 +5967,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>221</v>
@@ -5847,7 +5985,7 @@
         <v>6.5</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>126</v>
@@ -5859,7 +5997,7 @@
         <v>37</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M73" s="2" t="s">
         <v>27</v>
@@ -5878,10 +6016,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>19</v>
@@ -5896,7 +6034,7 @@
         <v>5.4</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>126</v>
@@ -5908,7 +6046,7 @@
         <v>37</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M74" s="2" t="s">
         <v>27</v>
@@ -5918,7 +6056,7 @@
         <v>28</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q74" s="6" t="s">
         <v>30</v>
@@ -5929,7 +6067,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>155</v>
@@ -5941,13 +6079,13 @@
         <v>20</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G75" s="5" t="n">
         <v>6.3</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>126</v>
@@ -5959,7 +6097,7 @@
         <v>37</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M75" s="2" t="s">
         <v>27</v>
@@ -5969,7 +6107,7 @@
         <v>28</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q75" s="6" t="s">
         <v>30</v>
@@ -5980,10 +6118,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>19</v>
@@ -5992,13 +6130,13 @@
         <v>20</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G76" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>23</v>
@@ -6010,7 +6148,7 @@
         <v>37</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M76" s="2" t="s">
         <v>27</v>
@@ -6020,7 +6158,7 @@
         <v>28</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q76" s="6" t="s">
         <v>30</v>
@@ -6031,25 +6169,25 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G77" s="5" t="n">
         <v>5.8</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>80</v>
@@ -6061,7 +6199,7 @@
         <v>37</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M77" s="2" t="s">
         <v>27</v>
@@ -6071,7 +6209,7 @@
         <v>60</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q77" s="6" t="s">
         <v>30</v>
@@ -6082,25 +6220,25 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G78" s="5" t="n">
         <v>7.4</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>80</v>
@@ -6112,7 +6250,7 @@
         <v>37</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M78" s="2" t="s">
         <v>27</v>
@@ -6122,7 +6260,7 @@
         <v>50</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q78" s="6" t="s">
         <v>30</v>
@@ -6133,19 +6271,19 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G79" s="5" t="n">
         <v>8</v>
@@ -6163,7 +6301,7 @@
         <v>37</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M79" s="2" t="s">
         <v>27</v>
@@ -6173,7 +6311,7 @@
         <v>50</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q79" s="6" t="s">
         <v>30</v>
@@ -6184,25 +6322,25 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>211</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G80" s="5" t="n">
         <v>8.2</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>80</v>
@@ -6214,7 +6352,7 @@
         <v>37</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>27</v>
@@ -6224,7 +6362,7 @@
         <v>50</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q80" s="6" t="s">
         <v>75</v>
@@ -6235,19 +6373,19 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="G81" s="5" t="n">
         <v>8.5</v>
@@ -6265,7 +6403,7 @@
         <v>37</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M81" s="2" t="s">
         <v>27</v>
@@ -6275,7 +6413,7 @@
         <v>60</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q81" s="6" t="s">
         <v>30</v>
@@ -6286,25 +6424,25 @@
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G82" s="5" t="n">
         <v>8.7</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>23</v>
@@ -6316,7 +6454,7 @@
         <v>37</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M82" s="2" t="s">
         <v>27</v>
@@ -6326,7 +6464,7 @@
         <v>60</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q82" s="6" t="s">
         <v>30</v>
@@ -6337,13 +6475,13 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>20</v>
@@ -6355,7 +6493,7 @@
         <v>8.5</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>80</v>
@@ -6367,7 +6505,7 @@
         <v>37</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M83" s="2" t="s">
         <v>27</v>
@@ -6377,7 +6515,7 @@
         <v>60</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q83" s="6" t="s">
         <v>30</v>
@@ -6388,13 +6526,13 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>20</v>
@@ -6406,7 +6544,7 @@
         <v>8.3</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>23</v>
@@ -6418,7 +6556,7 @@
         <v>37</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M84" s="2" t="s">
         <v>27</v>
@@ -6428,7 +6566,7 @@
         <v>60</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q84" s="6" t="s">
         <v>30</v>
@@ -6439,25 +6577,25 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G85" s="5" t="n">
         <v>7.9</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>80</v>
@@ -6469,7 +6607,7 @@
         <v>37</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M85" s="2" t="s">
         <v>27</v>
@@ -6479,7 +6617,7 @@
         <v>50</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q85" s="6" t="s">
         <v>30</v>
@@ -6490,13 +6628,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>20</v>
@@ -6508,7 +6646,7 @@
         <v>8</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I86" s="4" t="s">
         <v>74</v>
@@ -6520,7 +6658,7 @@
         <v>37</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M86" s="2" t="s">
         <v>27</v>
@@ -6541,25 +6679,25 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G87" s="5" t="n">
         <v>8.4</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>23</v>
@@ -6571,7 +6709,7 @@
         <v>37</v>
       </c>
       <c r="L87" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M87" s="2" t="s">
         <v>27</v>
@@ -6581,7 +6719,7 @@
         <v>28</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q87" s="6" t="s">
         <v>30</v>
@@ -6592,25 +6730,25 @@
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G88" s="5" t="n">
         <v>8</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>80</v>
@@ -6622,7 +6760,7 @@
         <v>37</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M88" s="2" t="s">
         <v>27</v>
@@ -6632,7 +6770,7 @@
         <v>60</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q88" s="6" t="s">
         <v>30</v>
@@ -6643,25 +6781,25 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G89" s="5" t="n">
         <v>8.4</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>126</v>
@@ -6673,7 +6811,7 @@
         <v>37</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M89" s="2" t="s">
         <v>27</v>
@@ -6692,25 +6830,25 @@
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G90" s="5" t="n">
         <v>9.3</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="I90" s="4" t="s">
         <v>126</v>
@@ -6722,7 +6860,7 @@
         <v>37</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M90" s="2" t="s">
         <v>27</v>
@@ -6732,7 +6870,7 @@
         <v>28</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Q90" s="6" t="s">
         <v>30</v>
@@ -6743,25 +6881,25 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G91" s="5" t="n">
         <v>8.3</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>80</v>
@@ -6773,7 +6911,7 @@
         <v>37</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M91" s="2" t="s">
         <v>27</v>
@@ -6783,7 +6921,7 @@
         <v>50</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q91" s="6" t="s">
         <v>30</v>
@@ -6794,13 +6932,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>106</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>20</v>
@@ -6812,7 +6950,7 @@
         <v>7.7</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>23</v>
@@ -6824,7 +6962,7 @@
         <v>103</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M92" s="2" t="s">
         <v>27</v>
@@ -6834,7 +6972,7 @@
         <v>28</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Q92" s="6" t="s">
         <v>30</v>
@@ -6845,25 +6983,25 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G93" s="5" t="n">
         <v>6.2</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="I93" s="4" t="s">
         <v>23</v>
@@ -6875,7 +7013,7 @@
         <v>25</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M93" s="2" t="s">
         <v>27</v>
@@ -6885,7 +7023,7 @@
         <v>28</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Q93" s="6" t="s">
         <v>30</v>
@@ -6896,13 +7034,13 @@
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>20</v>
@@ -6914,7 +7052,7 @@
         <v>8.4</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>23</v>
@@ -6926,7 +7064,7 @@
         <v>37</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M94" s="2" t="s">
         <v>27</v>
@@ -6936,7 +7074,7 @@
         <v>28</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Q94" s="6" t="s">
         <v>30</v>
@@ -6947,25 +7085,25 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G95" s="5" t="n">
         <v>8.5</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>23</v>
@@ -6977,7 +7115,7 @@
         <v>37</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M95" s="2" t="s">
         <v>27</v>
@@ -6987,7 +7125,7 @@
         <v>60</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Q95" s="6" t="s">
         <v>30</v>
@@ -6998,25 +7136,25 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G96" s="5" t="n">
         <v>8.4</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>23</v>
@@ -7028,7 +7166,7 @@
         <v>37</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M96" s="2" t="s">
         <v>27</v>
@@ -7047,25 +7185,25 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G97" s="5" t="n">
         <v>7.4</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>80</v>
@@ -7077,7 +7215,7 @@
         <v>37</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M97" s="2" t="s">
         <v>27</v>
@@ -7087,7 +7225,7 @@
         <v>60</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q97" s="6" t="s">
         <v>30</v>
@@ -7098,19 +7236,19 @@
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>222</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="G98" s="5" t="n">
         <v>8.3</v>
@@ -7128,7 +7266,7 @@
         <v>37</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M98" s="2" t="s">
         <v>27</v>
@@ -7138,7 +7276,7 @@
         <v>28</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="Q98" s="6" t="s">
         <v>30</v>
@@ -7149,13 +7287,13 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>20</v>
@@ -7167,7 +7305,7 @@
         <v>7.5</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>80</v>
@@ -7179,7 +7317,7 @@
         <v>37</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M99" s="2" t="s">
         <v>27</v>
@@ -7189,7 +7327,7 @@
         <v>28</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q99" s="6" t="s">
         <v>30</v>
@@ -7200,13 +7338,13 @@
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>20</v>
@@ -7218,7 +7356,7 @@
         <v>7.5</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>126</v>
@@ -7230,7 +7368,7 @@
         <v>37</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M100" s="2" t="s">
         <v>27</v>
@@ -7240,7 +7378,7 @@
         <v>28</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="Q100" s="6" t="s">
         <v>30</v>
@@ -7251,25 +7389,25 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G101" s="5" t="n">
         <v>8.7</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>74</v>
@@ -7281,7 +7419,7 @@
         <v>37</v>
       </c>
       <c r="L101" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M101" s="2" t="s">
         <v>27</v>
@@ -7291,7 +7429,7 @@
         <v>28</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="Q101" s="6" t="s">
         <v>30</v>
@@ -7302,13 +7440,13 @@
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>20</v>
@@ -7332,7 +7470,7 @@
         <v>37</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M102" s="2" t="s">
         <v>27</v>
@@ -7342,15 +7480,729 @@
         <v>60</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Q102" s="6" t="s">
         <v>30</v>
       </c>
     </row>
+    <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J103" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L103" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="M103" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P103" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="Q103" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="I104" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J104" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K104" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L104" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="M104" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P104" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q104" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J105" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K105" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L105" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P105" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="Q105" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J106" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K106" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L106" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P106" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="Q106" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="I107" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J107" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K107" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L107" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P107" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q107" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="I108" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J108" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K108" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L108" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="M108" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P108" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="Q108" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="I109" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J109" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K109" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L109" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="M109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P109" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q109" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="I110" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J110" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K110" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L110" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="M110" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P110" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q110" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I111" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="J111" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K111" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L111" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="M111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P111" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q111" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="I112" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="J112" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K112" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L112" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="M112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P112" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="Q112" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="J113" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K113" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L113" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P113" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="Q113" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I114" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="J114" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K114" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L114" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="M114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P114" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q114" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I115" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J115" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K115" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L115" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P115" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="Q115" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="I116" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J116" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K116" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L116" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="M116" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P116" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q116" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q102"/>
-  <conditionalFormatting sqref="I2:I102">
+  <autoFilter ref="A1:Q116"/>
+  <conditionalFormatting sqref="I2:I116">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>LEFT($I2,3)="Yes"</formula>
     </cfRule>
@@ -7364,7 +8216,7 @@
       <formula>LEFT($I2,2)="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O102">
+  <conditionalFormatting sqref="O2:O116">
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>$O2="High"</formula>
     </cfRule>
@@ -7375,21 +8227,21 @@
       <formula>$O2="Low"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:P102">
+  <conditionalFormatting sqref="A2:P116">
     <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
       <formula>$M2="Watched"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M102" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M116" type="list">
       <formula1>"Not watched,Watching,Watched,Unavailable"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="O2:O102" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="O2:O116" type="list">
       <formula1>"High,Medium,Low,—"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="N2:N102" type="decimal">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="N2:N116" type="decimal">
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
@@ -7496,6 +8348,20 @@
     <hyperlink ref="Q100" r:id="rId99" display="JustWatch"/>
     <hyperlink ref="Q101" r:id="rId100" display="JustWatch"/>
     <hyperlink ref="Q102" r:id="rId101" display="JustWatch"/>
+    <hyperlink ref="Q103" r:id="rId102" display="JustWatch"/>
+    <hyperlink ref="Q104" r:id="rId103" display="JustWatch"/>
+    <hyperlink ref="Q105" r:id="rId104" display="JustWatch"/>
+    <hyperlink ref="Q106" r:id="rId105" display="JustWatch"/>
+    <hyperlink ref="Q107" r:id="rId106" display="JustWatch"/>
+    <hyperlink ref="Q108" r:id="rId107" display="JustWatch"/>
+    <hyperlink ref="Q109" r:id="rId108" display="Netflix"/>
+    <hyperlink ref="Q110" r:id="rId109" display="JustWatch"/>
+    <hyperlink ref="Q111" r:id="rId110" display="JustWatch"/>
+    <hyperlink ref="Q112" r:id="rId111" display="JustWatch"/>
+    <hyperlink ref="Q113" r:id="rId112" display="Netflix"/>
+    <hyperlink ref="Q114" r:id="rId113" display="JustWatch"/>
+    <hyperlink ref="Q115" r:id="rId114" display="JustWatch"/>
+    <hyperlink ref="Q116" r:id="rId115" display="JustWatch"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7504,7 +8370,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId102"/>
+  <drawing r:id="rId116"/>
 </worksheet>
 </file>
 
@@ -7513,7 +8379,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -7522,12 +8388,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>448</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>449</v>
+        <v>495</v>
       </c>
       <c r="B2" s="8"/>
     </row>
@@ -7541,7 +8407,7 @@
         <v>80</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>450</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7549,7 +8415,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>451</v>
+        <v>497</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7557,7 +8423,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>452</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7565,7 +8431,7 @@
         <v>74</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>453</v>
+        <v>499</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7573,20 +8439,20 @@
         <v>126</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>454</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>455</v>
+        <v>501</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>456</v>
+        <v>502</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>457</v>
+        <v>503</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7594,7 +8460,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7602,7 +8468,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>459</v>
+        <v>505</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7610,15 +8476,15 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>460</v>
+        <v>506</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>461</v>
+        <v>507</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>462</v>
+        <v>508</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7626,15 +8492,15 @@
         <v>14</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>463</v>
+        <v>509</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>464</v>
+        <v>510</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>465</v>
+        <v>511</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7642,66 +8508,66 @@
         <v>16</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>466</v>
+        <v>512</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>467</v>
+        <v>513</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>468</v>
+        <v>514</v>
       </c>
       <c r="B22" s="12" t="n">
-        <f aca="false">COUNTA(Watchlist!$B$2:$B$102)</f>
-        <v>101</v>
+        <f aca="false">COUNTA(Watchlist!$B$2:$B$116)</f>
+        <v>115</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>469</v>
+        <v>515</v>
       </c>
       <c r="B23" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$I$2:$I$102,"Yes (verified)")</f>
-        <v>16</v>
+        <f aca="false">COUNTIF(Watchlist!$I$2:$I$116,"Yes (verified)")</f>
+        <v>19</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>470</v>
+        <v>516</v>
       </c>
       <c r="B24" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$I$2:$I$102,"Likely")</f>
+        <f aca="false">COUNTIF(Watchlist!$I$2:$I$116,"Likely")</f>
         <v>15</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>471</v>
+        <v>517</v>
       </c>
       <c r="B25" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$I$2:$I$102,"Unconfirmed")</f>
-        <v>36</v>
+        <f aca="false">COUNTIF(Watchlist!$I$2:$I$116,"Unconfirmed")</f>
+        <v>38</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>472</v>
+        <v>518</v>
       </c>
       <c r="B26" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$I$2:$I$102,"No (verified)")</f>
-        <v>7</v>
+        <f aca="false">COUNTIF(Watchlist!$I$2:$I$116,"No (verified)")</f>
+        <v>9</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>473</v>
+        <v>519</v>
       </c>
       <c r="B27" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$I$2:$I$102,"No")</f>
-        <v>27</v>
+        <f aca="false">COUNTIF(Watchlist!$I$2:$I$116,"No")</f>
+        <v>34</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7709,40 +8575,40 @@
         <v>24</v>
       </c>
       <c r="B28" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$J$2:$J$102,"Not streaming in India")</f>
-        <v>42</v>
+        <f aca="false">COUNTIF(Watchlist!$J$2:$J$116,"Not streaming in India")</f>
+        <v>51</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>474</v>
+        <v>520</v>
       </c>
       <c r="B29" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$O$2:$O$102,"High")</f>
+        <f aca="false">COUNTIF(Watchlist!$O$2:$O$116,"High")</f>
         <v>14</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>475</v>
+        <v>521</v>
       </c>
       <c r="B30" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$O$2:$O$102,"Medium")</f>
-        <v>19</v>
+        <f aca="false">COUNTIF(Watchlist!$O$2:$O$116,"Medium")</f>
+        <v>20</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>476</v>
+        <v>522</v>
       </c>
       <c r="B31" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$M$2:$M$102,"Watched")</f>
+        <f aca="false">COUNTIF(Watchlist!$M$2:$M$116,"Watched")</f>
         <v>8</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>477</v>
+        <v>523</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7750,7 +8616,7 @@
         <v>26</v>
       </c>
       <c r="B34" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$L$2:$L$102,"*Top 20 Hollywood*")</f>
+        <f aca="false">COUNTIF(Watchlist!$L$2:$L$116,"*Top 20 Hollywood*")</f>
         <v>20</v>
       </c>
     </row>
@@ -7759,7 +8625,7 @@
         <v>120</v>
       </c>
       <c r="B35" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$L$2:$L$102,"*Alien Signals*")</f>
+        <f aca="false">COUNTIF(Watchlist!$L$2:$L$116,"*Alien Signals*")</f>
         <v>9</v>
       </c>
     </row>
@@ -7768,7 +8634,7 @@
         <v>164</v>
       </c>
       <c r="B36" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$L$2:$L$102,"*Secret Societies*")</f>
+        <f aca="false">COUNTIF(Watchlist!$L$2:$L$116,"*Secret Societies*")</f>
         <v>12</v>
       </c>
     </row>
@@ -7777,106 +8643,124 @@
         <v>227</v>
       </c>
       <c r="B37" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$L$2:$L$102,"*Twisty Mystery*")</f>
+        <f aca="false">COUNTIF(Watchlist!$L$2:$L$116,"*Twisty Mystery*")</f>
         <v>12</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B38" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$L$2:$L$102,"*Space Adventure*")</f>
+        <f aca="false">COUNTIF(Watchlist!$L$2:$L$116,"*Space Adventure*")</f>
         <v>9</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B39" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$L$2:$L$102,"*Underrated Mystery*")</f>
+        <f aca="false">COUNTIF(Watchlist!$L$2:$L$116,"*Underrated Mystery*")</f>
         <v>9</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B40" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$L$2:$L$102,"*Time Loops*")</f>
+        <f aca="false">COUNTIF(Watchlist!$L$2:$L$116,"*Time Loops*")</f>
         <v>9</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B41" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$L$2:$L$102,"*South Mystery*")</f>
+        <f aca="false">COUNTIF(Watchlist!$L$2:$L$116,"*South Mystery*")</f>
         <v>1</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B42" s="12" t="n">
-        <f aca="false">COUNTIF(Watchlist!$L$2:$L$102,"*Action Web Series*")</f>
+        <f aca="false">COUNTIF(Watchlist!$L$2:$L$116,"*Action Web Series*")</f>
         <v>25</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9" t="s">
+    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="B43" s="12" t="n">
+        <f aca="false">COUNTIF(Watchlist!$L$2:$L$116,"*Psychological Experiments*")</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="11" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10" t="s">
-        <v>479</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>480</v>
+      <c r="B44" s="12" t="n">
+        <f aca="false">COUNTIF(Watchlist!$L$2:$L$116,"*Lonely Astronauts*")</f>
+        <v>9</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>482</v>
+      <c r="A46" s="9" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>483</v>
+        <v>525</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>484</v>
+        <v>526</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>485</v>
+        <v>527</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>486</v>
+        <v>528</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>487</v>
+        <v>529</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>488</v>
+        <v>530</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>338</v>
+        <v>531</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>489</v>
+        <v>532</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>535</v>
       </c>
     </row>
   </sheetData>
